--- a/요구사항_정의서/요구사항_정의서_v9.xlsx
+++ b/요구사항_정의서/요구사항_정의서_v9.xlsx
@@ -3017,29 +3017,29 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>복약관리대상자로서, 저신뢰 항목을 확인한 후에도 궁금하면 관련 가이드의 챗봇으로 바로 이어서 물어보고 싶다.</t>
+          <t>복약관리대상자로서, 저신뢰 항목을 확인한 후에도 궁금하면 조건 없이 언제든 챗봇으로 바로 이어서 물어보고 싶다.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>저신뢰 항목 확인 후에도 문제가 있으면, 해당 기록의 가이드가 이미 생성된 경우 그 guide_result_id로 챗봇(REQ-021, /chat)에 진입하는 버튼을 노출해야 한다. 가이드가 아직 없으면 챗봇을 열지 않고 '가이드가 생성되면 챗봇으로 질문할 수 있다'는 안내 문구만 표시한다. /chat 요청 스키마는 확장하지 않고 기존 guide_result_id 기반을 그대로 사용한다.</t>
+          <t>[제품 결정, 2026-07-21] 애초 설계는 '가이드가 이미 생성된 경우에만 guide_result_id로 챗봇 진입 버튼을 노출하고, 없으면 안내 문구만 표시'하는 조건부 분기였으나, 실제로는 챗봇이 patient_id 기반으로 가이드 유무와 무관하게 항상 열려 있다는 사실을 확인한 뒤 이 편이 더 낫다고 판단해 조건부 분기 자체를 없애기로 결정했다. 챗봇 진입 버튼은 가이드 존재 여부와 무관하게 항상 노출된다.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>• 가이드 존재 시 guide_result_id로 챗봇 진입 버튼 노출
-• 가이드 미존재 시 안내 문구만 표시
-• /chat 스키마 미확장</t>
+          <t>• 챗봇 진입 버튼은 가이드 존재 여부와 무관하게 항상 노출됨
+• '가이드 없으면 안내 문구만 표시'하는 별도 분기 없음(제거됨)
+• /chat 요청 스키마 변경 없음(patient_id 기반 그대로)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>미구현</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>챗봇 자체는 guide_result_id 없이도 patient_id 기반으로 이미 항상 열려 있어, REQ-048이 정의한 조건부 버튼 노출·안내 문구 분기는 별도로 존재하지 않음(프론트 확인 필요)</t>
+          <t>Result.tsx/PrescriptionReview.tsx의 챗봇 진입 버튼이 guide_result_id 유무와 무관하게 항상 노출되는 현재 동작을 그대로 목표 사양으로 확정했다(2026-07-21 제품 결정). 조건부 분기를 추가 개발할 필요가 없어졌으므로 현재 코드가 이미 인수조건을 충족한다.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>기존 REQ-021 챗봇 재사용; 스키마 변경 없는 UI 규칙</t>
+          <t>[2026-07-21 정정] v9 최초 초안은 원래 설계(조건부 분기)를 기준으로 '미구현'이라고 판정했으나, 조건부 분기 자체를 없애기로 제품 결정하면서 현재 동작(항상 열림)이 곧 요구사항이 됐다 — '완료'로 재정정. 자가진단(REQ-005/006/007)과 달리 기능을 없애는 게 아니라 조건을 단순화하는 결정이라는 점에 유의</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
 3. 추출 텍스트를 약품명·용량·복용횟수·진단명·약효분류·신뢰도 구조로 변환한다. (REQ-010)
 4. [정정] 신뢰도와 무관하게 항상 review_required로 분류하고 확인·수정 전에는 가이드를 확정하지 않는다. (REQ-011 — v6은 '신뢰도 0.80 미만만'이었으나 실제로는 '전부 확인' 정책으로 바뀜, 3라운드 감사로 정정)
 4a. 확인·수정 시 입력한 약물명이 사전과 다르면 typo_suggestion(오타 제안)을 응답에 포함한다. (REQ-047)
-4b. 확인 후에도 문제가 있으면 가이드가 이미 있을 때 guide_result_id로 챗봇 연결 버튼을 노출하고, 없으면 안내 문구만 표시한다. (REQ-048)
+4b. 확인 후에도 문제가 있으면 가이드 존재 여부와 무관하게 언제든 챗봇으로 이어서 질문할 수 있다. (REQ-048, [2026-07-21 제품 결정] 원래는 guide_result_id 유무로 조건부 노출/안내 문구 분기를 두려 했으나, 조건 없이 항상 여는 편으로 결정 — 현재 코드 동작 그대로 사양 확정)
 5. RAG+LLM으로 복용법·주의사항·병용금기 가이드를 생성하며 출처(source_refs)를 포함한다. 의료 고지(disclaimer)는 API 응답 필드가 아니라 프론트 하드코딩이다(REQ-032, 부분). (REQ-012)
 6. 사용자가 가이드 문맥에서 추가 질문하면 SSE로 실시간 답변을 받는다(챗봇 POST /chat/ask/stream, 인가 적용됨). (REQ-021)</t>
         </is>
